--- a/results/Int Task Remove ACC -0.6/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_1_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7962708091640494</v>
+        <v>0.8161336691095329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7950363600350867</v>
+        <v>0.8191845165671598</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7992041349518501</v>
+        <v>0.8096028220291823</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7957437537138168</v>
+        <v>0.815177461494204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7970429057845939</v>
+        <v>0.8151167199569904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8040711920998274</v>
+        <v>0.8095166143195345</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8101728870150816</v>
+        <v>0.8069516991596164</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8163000481027701</v>
+        <v>0.7995900889429652</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8219510860850947</v>
+        <v>0.792122652631976</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8106842854852249</v>
+        <v>0.792122652631976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8136332682531149</v>
+        <v>0.792122652631976</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8058366580836234</v>
+        <v>0.7903317204757458</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.796492081906756</v>
+        <v>0.7931396017845185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7872533318242269</v>
+        <v>0.7905746866246003</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7879214887335767</v>
+        <v>0.790731445063807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7896222517755582</v>
+        <v>0.8020531394131463</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7935881836959905</v>
+        <v>0.8056506607056959</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7929709591315093</v>
+        <v>0.7948992199805702</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7709115946539902</v>
+        <v>0.8010261924299444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7402522094262566</v>
+        <v>0.7821646246569141</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7425585014572309</v>
+        <v>0.7871886288824124</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7125023815587184</v>
+        <v>0.7813357479037568</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7249036529809569</v>
+        <v>0.7786846250341907</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7229363440008301</v>
+        <v>0.782346849268555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7229363440008301</v>
+        <v>0.782346849268555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7203714288409119</v>
+        <v>0.7799426539524443</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7129960480273149</v>
+        <v>0.7657366797770295</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7067983362100676</v>
+        <v>0.7493342010695793</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6803401148807334</v>
+        <v>0.7392312988691132</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6781945426935665</v>
+        <v>0.7381634173717024</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.676474161266895</v>
+        <v>0.7381634173717024</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6734644369617913</v>
+        <v>0.7335078237740867</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.68304443375494</v>
+        <v>0.7369780142044651</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6932237344727088</v>
+        <v>0.7172209803533196</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6932237344727088</v>
+        <v>0.7161138620865284</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.696578289616404</v>
+        <v>0.7147735868632279</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6966997726908313</v>
+        <v>0.7386806636295898</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7095988606245814</v>
+        <v>0.7384318496929911</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7085426747026589</v>
+        <v>0.7455308753760976</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7018041368382333</v>
+        <v>0.7093868311592768</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.698792337511672</v>
+        <v>0.6808984842911443</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6897201550606944</v>
+        <v>0.6630165152844194</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6897201550606944</v>
+        <v>0.6746634220876602</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6675334597210039</v>
+        <v>0.6524629561510238</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6675334597210039</v>
+        <v>0.6392269601878837</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6628484385463531</v>
+        <v>0.6644469596219689</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6672708751874593</v>
+        <v>0.665838167190138</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6664361506465578</v>
+        <v>0.6695160484045914</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6688658121351028</v>
+        <v>0.6739756467936202</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7198036275147845</v>
+        <v>0.6475642077662394</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7182909368721881</v>
+        <v>0.6796012186035105</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7134804712185092</v>
+        <v>0.6743753713816814</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6973228450430566</v>
+        <v>0.6644311140035652</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7042277619007196</v>
+        <v>0.6922356469822586</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7196798807805853</v>
+        <v>0.6913049055393641</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7341365552757421</v>
+        <v>0.6910266640257303</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7175184629750149</v>
+        <v>0.6937385284325099</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7175184629750149</v>
+        <v>0.6972439942276676</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7158901370457353</v>
+        <v>0.6860302009941239</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7227658149646774</v>
+        <v>0.6893907925638776</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7320790771813663</v>
+        <v>0.6941463644680871</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7225777425652924</v>
+        <v>0.6840161097120436</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7219273176574894</v>
+        <v>0.7011220206936231</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7219273176574894</v>
+        <v>0.7007222961055619</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6228418362053517</v>
+        <v>0.7035733755883158</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6029808626430114</v>
+        <v>0.6621446289955952</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5958935325353933</v>
+        <v>0.6566660064325665</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5416266281844506</v>
+        <v>0.6308657555436085</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5511573903775596</v>
+        <v>0.630516963300416</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5625554832442018</v>
+        <v>0.6581315374965809</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.563456797110061</v>
+        <v>0.6588781679446912</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5997242107844525</v>
+        <v>0.6763092913801723</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5601394037142884</v>
+        <v>0.6788134650028768</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5513924337172122</v>
+        <v>0.6827695877309641</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5513924337172122</v>
+        <v>0.6758390160625525</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5500972430510361</v>
+        <v>0.675889948407421</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5570376239117927</v>
+        <v>0.6377021966931703</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5609075389302322</v>
+        <v>0.5324778585778558</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5397866500664951</v>
+        <v>0.5324778585778558</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5389519255255936</v>
+        <v>0.5135476264584099</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5371864595417976</v>
+        <v>0.5076085377701065</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.533228450430567</v>
+        <v>0.5087822453618555</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5196180074134857</v>
+        <v>0.5111041943729191</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5202646595550022</v>
+        <v>0.5093740037539024</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5005312054931477</v>
+        <v>0.5032174150891787</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4948096167812644</v>
+        <v>0.504608622657348</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4948096167812644</v>
+        <v>0.5034290672778547</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4948096167812644</v>
+        <v>0.5044969487752657</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4962008243494336</v>
+        <v>0.5045871178895145</v>
       </c>
     </row>
   </sheetData>
